--- a/trendstrategy_results_equityV2.xlsx
+++ b/trendstrategy_results_equityV2.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="192">
   <si>
     <t>項目</t>
   </si>
@@ -42,7 +42,7 @@
     <t>總報酬率</t>
   </si>
   <si>
-    <t>交易筆數 (2026起)</t>
+    <t>2026起交易筆數 (不含保持)</t>
   </si>
   <si>
     <t>2026-01-02</t>
@@ -87,6 +87,9 @@
     <t>總資產</t>
   </si>
   <si>
+    <t>備註</t>
+  </si>
+  <si>
     <t>順達(3211), 璟德(3152), 威剛(3260)</t>
   </si>
   <si>
@@ -132,6 +135,51 @@
     <t>南俊國際(6584), 頎邦(6147)</t>
   </si>
   <si>
+    <t>今日觸發 順達(3211) 停損機制出場。</t>
+  </si>
+  <si>
+    <t>今日觸發 威剛(3260) 停損機制出場。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】群聯(8299), 欣銓(3264), 精材(3374) 【賣出】璟德(3152) </t>
+  </si>
+  <si>
+    <t>今日觸發 欣銓(3264) 停損機制出場。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】世界(5347), 昇達科(3491), 南亞(1303) 【賣出】群聯(8299), 精材(3374) </t>
+  </si>
+  <si>
+    <t>今日觸發 世界(5347) 停損機制出場。</t>
+  </si>
+  <si>
+    <t>今日觸發 南亞(1303) 停損機制出場。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】精測(6510), 波若威(3163) 【續抱】昇達科(3491) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】萬潤(6187) 【賣出】精測(6510) 【續抱】波若威(3163), 昇達科(3491) </t>
+  </si>
+  <si>
+    <t>今日觸發 昇達科(3491) 停損機制出場。；今日觸發 波若威(3163) 停損機制出場。</t>
+  </si>
+  <si>
+    <t>今日觸發 萬潤(6187) 停損機制出場。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】萬潤(6187), 波若威(3163), 致茂(2360) </t>
+  </si>
+  <si>
+    <t>今日觸發 波若威(3163) 停損機制出場。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】南俊國際(6584), 頎邦(6147) 【賣出】致茂(2360) 【續抱】萬潤(6187) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">再平衡日，建議次日交易指令：【買進】聯亞(3081), 印能科技(7734) 【賣出】南俊國際(6584) 【續抱】頎邦(6147) </t>
+  </si>
+  <si>
     <t>訊號日期</t>
   </si>
   <si>
@@ -372,16 +420,16 @@
     <t>再平衡</t>
   </si>
   <si>
-    <t>符合趨勢</t>
-  </si>
-  <si>
-    <t>趨勢持續</t>
-  </si>
-  <si>
-    <t>停損賣出：順達 (觸發停損：價格由波段高點回落 9.99%)</t>
-  </si>
-  <si>
-    <t>停損賣出：威剛 (觸發停損：價格由波段高點回落 9.99%)</t>
+    <t>再平衡買入</t>
+  </si>
+  <si>
+    <t>續抱</t>
+  </si>
+  <si>
+    <t>停損賣出：順達 (觸發停損：價格由高點回落 9.99%)</t>
+  </si>
+  <si>
+    <t>停損賣出：威剛 (觸發停損：價格由高點回落 9.99%)</t>
   </si>
   <si>
     <t>再平衡賣出：璟德</t>
@@ -396,7 +444,7 @@
     <t>買進標的：精材</t>
   </si>
   <si>
-    <t>停損賣出：欣銓 (觸發停損：價格由波段高點回落 9.99%)</t>
+    <t>停損賣出：欣銓 (觸發停損：價格由高點回落 9.99%)</t>
   </si>
   <si>
     <t>再平衡賣出：群聯</t>
@@ -414,10 +462,10 @@
     <t>買進標的：南亞</t>
   </si>
   <si>
-    <t>停損賣出：世界 (觸發停損：價格由波段高點回落 9.99%)</t>
-  </si>
-  <si>
-    <t>停損賣出：南亞 (觸發停損：價格由波段高點回落 9.99%)</t>
+    <t>停損賣出：世界 (觸發停損：價格由高點回落 9.99%)</t>
+  </si>
+  <si>
+    <t>停損賣出：南亞 (觸發停損：價格由高點回落 9.99%)</t>
   </si>
   <si>
     <t>買進標的：精測</t>
@@ -438,13 +486,13 @@
     <t>保持持有：波若威</t>
   </si>
   <si>
-    <t>停損賣出：昇達科 (觸發停損：價格由波段高點回落 9.99%)</t>
-  </si>
-  <si>
-    <t>停損賣出：波若威 (觸發停損：價格由波段高點回落 9.99%)</t>
-  </si>
-  <si>
-    <t>停損賣出：萬潤 (觸發停損：價格由波段高點回落 9.99%)</t>
+    <t>停損賣出：昇達科 (觸發停損：價格由高點回落 9.99%)</t>
+  </si>
+  <si>
+    <t>停損賣出：波若威 (觸發停損：價格由高點回落 9.99%)</t>
+  </si>
+  <si>
+    <t>停損賣出：萬潤 (觸發停損：價格由高點回落 9.99%)</t>
   </si>
   <si>
     <t>買進標的：致茂</t>
@@ -489,55 +537,55 @@
     <t>賣出原因</t>
   </si>
   <si>
-    <t>動能訊號符合，ROC: 34.77%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 33.15%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 34.36%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 44.75%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 59.91%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 38.87%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 57.19%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 38.67%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 63.05%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 40.99%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 31.11%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 50.27%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 50.76%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 45.71%</t>
-  </si>
-  <si>
-    <t>動能訊號符合，ROC: 74.94%</t>
-  </si>
-  <si>
-    <t>觸發停損：價格由波段高點回落 9.99%</t>
-  </si>
-  <si>
-    <t>再平衡賣出：排名落後或未過濾網</t>
+    <t>動能符合, ROC:34.77%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:33.15%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:34.36%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:44.75%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:59.91%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:38.87%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:57.19%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:38.67%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:63.05%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:40.99%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:31.11%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:50.27%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:50.76%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:45.71%</t>
+  </si>
+  <si>
+    <t>動能符合, ROC:74.94%</t>
+  </si>
+  <si>
+    <t>觸發停損：價格由高點回落 9.99%</t>
+  </si>
+  <si>
+    <t>再平衡賣出</t>
   </si>
   <si>
     <t>持有股數</t>
@@ -612,7 +660,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>2026 權益曲線 (自 2026/01/02 起)</a:t>
+              <a:t>2026 淨值走勢圖 (起始日: 2026/01/02)</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2142,10 +2190,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -2164,13 +2212,16 @@
       <c r="F1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1">
         <v>46024</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2185,12 +2236,12 @@
         <v>146516889.6059999</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="1">
         <v>46027</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2205,12 +2256,12 @@
         <v>146528799.6059999</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="1">
         <v>46028</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2225,12 +2276,12 @@
         <v>146342969.6059999</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="1">
         <v>46029</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2245,18 +2296,18 @@
         <v>146326799.6059999</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="1">
         <v>46030</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>125533576.2684999</v>
+        <v>116886509.6059999</v>
       </c>
       <c r="E6">
         <v>28933360</v>
@@ -2264,19 +2315,22 @@
       <c r="F6">
         <v>145819869.6059999</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="1">
         <v>46031</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>135827891.4587499</v>
+        <v>125533576.2684999</v>
       </c>
       <c r="E7">
         <v>19056240</v>
@@ -2284,19 +2338,22 @@
       <c r="F7">
         <v>144589816.2684999</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="1">
         <v>46034</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>118047396.1337499</v>
+        <v>135827891.4587499</v>
       </c>
       <c r="E8">
         <v>10263000</v>
@@ -2304,13 +2361,16 @@
       <c r="F8">
         <v>146090891.4587499</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="1">
         <v>46035</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2325,12 +2385,12 @@
         <v>146727396.1337499</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="1">
         <v>46036</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2345,12 +2405,12 @@
         <v>147494396.1337499</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="1">
         <v>46037</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2365,12 +2425,12 @@
         <v>147714396.1337499</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="1">
         <v>46038</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2385,12 +2445,12 @@
         <v>148051396.1337499</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="1">
         <v>46041</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2405,12 +2465,12 @@
         <v>149741396.1337499</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="1">
         <v>46042</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2425,18 +2485,18 @@
         <v>150580396.1337499</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="1">
         <v>46043</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>129510446.6837499</v>
+        <v>118047396.1337499</v>
       </c>
       <c r="E15">
         <v>30191000</v>
@@ -2444,13 +2504,16 @@
       <c r="F15">
         <v>148238396.1337499</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="1">
         <v>46044</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -2465,18 +2528,18 @@
         <v>149361446.6837499</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="1">
         <v>46045</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>121072575.4862499</v>
+        <v>129510446.6837499</v>
       </c>
       <c r="E17">
         <v>19912000</v>
@@ -2484,13 +2547,16 @@
       <c r="F17">
         <v>149422446.6837499</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1">
         <v>46048</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2505,12 +2571,12 @@
         <v>149778275.4862499</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="1">
         <v>46049</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2525,12 +2591,12 @@
         <v>150510175.4862499</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="1">
         <v>46050</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2545,12 +2611,12 @@
         <v>150857075.4862499</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="1">
         <v>46051</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2565,18 +2631,18 @@
         <v>149077675.4862499</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:7">
       <c r="A22" s="1">
         <v>46052</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>130313502.6362499</v>
+        <v>121072575.4862499</v>
       </c>
       <c r="E22">
         <v>27701900</v>
@@ -2584,19 +2650,22 @@
       <c r="F22">
         <v>148774475.4862499</v>
       </c>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="1">
         <v>46055</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>139107416.6112499</v>
+        <v>130313502.6362499</v>
       </c>
       <c r="E23">
         <v>17862600</v>
@@ -2604,13 +2673,16 @@
       <c r="F23">
         <v>148176102.6362499</v>
       </c>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" s="1">
         <v>46056</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -2625,12 +2697,12 @@
         <v>149347416.6112499</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:7">
       <c r="A25" s="1">
         <v>46057</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -2645,18 +2717,18 @@
         <v>150147416.6112499</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:7">
       <c r="A26" s="1">
         <v>46058</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>121902935.1112499</v>
+        <v>139107416.6112499</v>
       </c>
       <c r="E26">
         <v>10240000</v>
@@ -2664,13 +2736,16 @@
       <c r="F26">
         <v>149347416.6112499</v>
       </c>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="1">
         <v>46059</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2685,12 +2760,12 @@
         <v>149122935.1112499</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:7">
       <c r="A28" s="1">
         <v>46062</v>
       </c>
       <c r="B28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -2705,12 +2780,12 @@
         <v>150982935.1112499</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:7">
       <c r="A29" s="1">
         <v>46063</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -2725,12 +2800,12 @@
         <v>151542935.1112499</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:7">
       <c r="A30" s="1">
         <v>46064</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -2745,12 +2820,12 @@
         <v>152842935.1112499</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:7">
       <c r="A31" s="1">
         <v>46076</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -2765,12 +2840,12 @@
         <v>154442935.1112499</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:7">
       <c r="A32" s="1">
         <v>46077</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -2785,12 +2860,12 @@
         <v>156012935.1112499</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:7">
       <c r="A33" s="1">
         <v>46078</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -2805,12 +2880,12 @@
         <v>157532935.1112499</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:7">
       <c r="A34" s="1">
         <v>46079</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -2825,18 +2900,18 @@
         <v>157722935.1112499</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:7">
       <c r="A35" s="1">
         <v>46083</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35">
-        <v>122432862.7862499</v>
+        <v>121902935.1112499</v>
       </c>
       <c r="E35">
         <v>37220000</v>
@@ -2844,13 +2919,16 @@
       <c r="F35">
         <v>159122935.1112499</v>
       </c>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" s="1">
         <v>46084</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -2865,18 +2943,18 @@
         <v>158561862.7862499</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:7">
       <c r="A37" s="1">
         <v>46085</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>147720467.7862499</v>
+        <v>122432862.7862499</v>
       </c>
       <c r="E37">
         <v>32820000</v>
@@ -2884,13 +2962,16 @@
       <c r="F37">
         <v>155252862.7862499</v>
       </c>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" s="1">
         <v>46086</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -2905,12 +2986,12 @@
         <v>154309467.7862499</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:7">
       <c r="A39" s="1">
         <v>46087</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -2925,18 +3006,18 @@
         <v>154210467.7862499</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:7">
       <c r="A40" s="1">
         <v>46090</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>153557524.0112499</v>
+        <v>147720467.7862499</v>
       </c>
       <c r="E40">
         <v>5841000</v>
@@ -2944,8 +3025,11 @@
       <c r="F40">
         <v>153561467.7862499</v>
       </c>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1">
         <v>46091</v>
       </c>
@@ -2962,7 +3046,7 @@
         <v>153557524.0112499</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:7">
       <c r="A42" s="1">
         <v>46092</v>
       </c>
@@ -2979,7 +3063,7 @@
         <v>153557524.0112499</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:7">
       <c r="A43" s="1">
         <v>46093</v>
       </c>
@@ -2996,15 +3080,15 @@
         <v>153557524.0112499</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:7">
       <c r="A44" s="1">
         <v>46094</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>125701886.2112499</v>
+        <v>153557524.0112499</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3012,13 +3096,16 @@
       <c r="F44">
         <v>153557524.0112499</v>
       </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" s="1">
         <v>46097</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3033,12 +3120,12 @@
         <v>153517886.2112499</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:7">
       <c r="A46" s="1">
         <v>46098</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3053,12 +3140,12 @@
         <v>152184886.2112499</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:7">
       <c r="A47" s="1">
         <v>46099</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -3073,12 +3160,12 @@
         <v>153071886.2112499</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:7">
       <c r="A48" s="1">
         <v>46100</v>
       </c>
       <c r="B48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3093,12 +3180,12 @@
         <v>154136886.2112499</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:7">
       <c r="A49" s="1">
         <v>46101</v>
       </c>
       <c r="B49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -3113,18 +3200,18 @@
         <v>154978886.2112499</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:7">
       <c r="A50" s="1">
         <v>46104</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>134054760.4612499</v>
+        <v>125701886.2112499</v>
       </c>
       <c r="E50">
         <v>28120000</v>
@@ -3132,13 +3219,16 @@
       <c r="F50">
         <v>153821886.2112499</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" s="1">
         <v>46105</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -3153,12 +3243,12 @@
         <v>154231760.4612499</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:7">
       <c r="A52" s="1">
         <v>46106</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -3173,18 +3263,18 @@
         <v>156219760.4612499</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:7">
       <c r="A53" s="1">
         <v>46107</v>
       </c>
       <c r="B53" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53">
-        <v>124330317.0112499</v>
+        <v>134054760.4612499</v>
       </c>
       <c r="E53">
         <v>22047000</v>
@@ -3192,13 +3282,16 @@
       <c r="F53">
         <v>156101760.4612499</v>
       </c>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" s="1">
         <v>46108</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3213,12 +3306,12 @@
         <v>156258317.0112499</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:7">
       <c r="A55" s="1">
         <v>46111</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -3233,18 +3326,18 @@
         <v>155249817.0112499</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:7">
       <c r="A56" s="1">
         <v>46112</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>135862062.2362499</v>
+        <v>124330317.0112499</v>
       </c>
       <c r="E56">
         <v>28113500</v>
@@ -3252,13 +3345,16 @@
       <c r="F56">
         <v>152443817.0112499</v>
       </c>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -3273,12 +3369,12 @@
         <v>155172062.2362499</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:7">
       <c r="A58" s="1">
         <v>46114</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -3293,12 +3389,12 @@
         <v>155482062.2362499</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:7">
       <c r="A59" s="1">
         <v>46119</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -3313,12 +3409,12 @@
         <v>156623062.2362499</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:7">
       <c r="A60" s="1">
         <v>46120</v>
       </c>
       <c r="B60" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -3333,12 +3429,12 @@
         <v>158663562.2362499</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:7">
       <c r="A61" s="1">
         <v>46121</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -3351,6 +3447,29 @@
       </c>
       <c r="F61">
         <v>157348562.2362499</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B62" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62">
+        <v>135862062.2362499</v>
+      </c>
+      <c r="E62">
+        <v>23314000</v>
+      </c>
+      <c r="F62">
+        <v>159176062.2362499</v>
+      </c>
+      <c r="G62" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3365,40 +3484,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="H1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="I1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="K1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="L1" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -3406,10 +3525,10 @@
         <v>46030</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D2">
         <v>299.5</v>
@@ -3418,13 +3537,13 @@
         <v>29000</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3436,7 +3555,7 @@
         <v>26056.5</v>
       </c>
       <c r="L2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3444,10 +3563,10 @@
         <v>46031</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D3">
         <v>265.13</v>
@@ -3456,13 +3575,13 @@
         <v>39000</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="H3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3474,7 +3593,7 @@
         <v>31020.21</v>
       </c>
       <c r="L3" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -3482,10 +3601,10 @@
         <v>46034</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D4">
         <v>166.5</v>
@@ -3494,13 +3613,13 @@
         <v>66000</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="H4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3512,7 +3631,7 @@
         <v>32967</v>
       </c>
       <c r="L4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -3520,10 +3639,10 @@
         <v>46034</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D5">
         <v>1770</v>
@@ -3532,13 +3651,13 @@
         <v>5000</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="G5" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I5">
         <v>12611.25</v>
@@ -3550,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -3558,10 +3677,10 @@
         <v>46034</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D6">
         <v>130.5</v>
@@ -3570,13 +3689,13 @@
         <v>76000</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I6">
         <v>14133.15</v>
@@ -3588,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3596,10 +3715,10 @@
         <v>46034</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D7">
         <v>177</v>
@@ -3608,13 +3727,13 @@
         <v>56000</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I7">
         <v>14124.6</v>
@@ -3626,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -3634,10 +3753,10 @@
         <v>46043</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D8">
         <v>151.5</v>
@@ -3646,13 +3765,13 @@
         <v>76000</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="H8" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3664,7 +3783,7 @@
         <v>34542</v>
       </c>
       <c r="L8" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -3672,10 +3791,10 @@
         <v>46045</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D9">
         <v>2075</v>
@@ -3684,13 +3803,13 @@
         <v>5000</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -3702,7 +3821,7 @@
         <v>31125</v>
       </c>
       <c r="L9" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -3710,10 +3829,10 @@
         <v>46045</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <v>179</v>
@@ -3722,13 +3841,13 @@
         <v>56000</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="H10" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -3740,7 +3859,7 @@
         <v>30072</v>
       </c>
       <c r="L10" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -3748,10 +3867,10 @@
         <v>46045</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D11">
         <v>145</v>
@@ -3760,13 +3879,13 @@
         <v>68000</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I11">
         <v>14050.5</v>
@@ -3778,7 +3897,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3786,10 +3905,10 @@
         <v>46045</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D12">
         <v>1120</v>
@@ -3798,13 +3917,13 @@
         <v>8000</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I12">
         <v>12768</v>
@@ -3816,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -3824,10 +3943,10 @@
         <v>46045</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D13">
         <v>81.7</v>
@@ -3836,13 +3955,13 @@
         <v>121000</v>
       </c>
       <c r="F13" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I13">
         <v>14087.1225</v>
@@ -3854,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3862,10 +3981,10 @@
         <v>46052</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D14">
         <v>136.5</v>
@@ -3874,13 +3993,13 @@
         <v>68000</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H14" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -3892,7 +4011,7 @@
         <v>27846</v>
       </c>
       <c r="L14" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -3900,10 +4019,10 @@
         <v>46055</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D15">
         <v>73</v>
@@ -3912,13 +4031,13 @@
         <v>121000</v>
       </c>
       <c r="F15" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G15" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H15" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -3930,7 +4049,7 @@
         <v>26499</v>
       </c>
       <c r="L15" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -3938,10 +4057,10 @@
         <v>46058</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D16">
         <v>3700</v>
@@ -3950,13 +4069,13 @@
         <v>2000</v>
       </c>
       <c r="F16" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I16">
         <v>10545</v>
@@ -3968,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -3976,10 +4095,10 @@
         <v>46058</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D17">
         <v>489</v>
@@ -3988,13 +4107,13 @@
         <v>20000</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G17" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H17" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I17">
         <v>13936.5</v>
@@ -4006,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -4014,10 +4133,10 @@
         <v>46058</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D18">
         <v>1280</v>
@@ -4026,13 +4145,13 @@
         <v>8000</v>
       </c>
       <c r="F18" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H18" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4044,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -4052,10 +4171,10 @@
         <v>46083</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D19">
         <v>3580</v>
@@ -4064,13 +4183,13 @@
         <v>2000</v>
       </c>
       <c r="F19" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H19" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4082,7 +4201,7 @@
         <v>21480</v>
       </c>
       <c r="L19" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -4090,10 +4209,10 @@
         <v>46083</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D20">
         <v>599</v>
@@ -4102,13 +4221,13 @@
         <v>11000</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I20">
         <v>9389.325000000001</v>
@@ -4120,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -4128,10 +4247,10 @@
         <v>46083</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D21">
         <v>1725</v>
@@ -4140,13 +4259,13 @@
         <v>8000</v>
       </c>
       <c r="F21" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -4158,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -4166,10 +4285,10 @@
         <v>46083</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D22">
         <v>808</v>
@@ -4178,13 +4297,13 @@
         <v>20000</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -4196,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -4204,10 +4323,10 @@
         <v>46085</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D23">
         <v>1380</v>
@@ -4216,13 +4335,13 @@
         <v>8000</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -4234,7 +4353,7 @@
         <v>33120</v>
       </c>
       <c r="L23" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -4242,10 +4361,10 @@
         <v>46085</v>
       </c>
       <c r="B24" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D24">
         <v>718</v>
@@ -4254,13 +4373,13 @@
         <v>20000</v>
       </c>
       <c r="F24" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H24" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4272,7 +4391,7 @@
         <v>43080</v>
       </c>
       <c r="L24" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -4280,10 +4399,10 @@
         <v>46090</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D25">
         <v>533</v>
@@ -4292,13 +4411,13 @@
         <v>11000</v>
       </c>
       <c r="F25" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H25" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -4310,7 +4429,7 @@
         <v>17589</v>
       </c>
       <c r="L25" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -4318,10 +4437,10 @@
         <v>46094</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D26">
         <v>732</v>
@@ -4330,13 +4449,13 @@
         <v>13000</v>
       </c>
       <c r="F26" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="G26" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I26">
         <v>13560.3</v>
@@ -4348,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -4356,10 +4475,10 @@
         <v>46094</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D27">
         <v>960</v>
@@ -4368,13 +4487,13 @@
         <v>10000</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G27" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I27">
         <v>13680</v>
@@ -4386,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -4394,10 +4513,10 @@
         <v>46094</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D28">
         <v>1450</v>
@@ -4406,13 +4525,13 @@
         <v>6000</v>
       </c>
       <c r="F28" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I28">
         <v>12397.5</v>
@@ -4424,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -4432,10 +4551,10 @@
         <v>46104</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D29">
         <v>839</v>
@@ -4444,13 +4563,13 @@
         <v>10000</v>
       </c>
       <c r="F29" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="H29" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -4462,7 +4581,7 @@
         <v>25170</v>
       </c>
       <c r="L29" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -4470,10 +4589,10 @@
         <v>46107</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D30">
         <v>1615</v>
@@ -4482,13 +4601,13 @@
         <v>6000</v>
       </c>
       <c r="F30" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="H30" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -4500,7 +4619,7 @@
         <v>29070</v>
       </c>
       <c r="L30" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -4508,10 +4627,10 @@
         <v>46107</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D31">
         <v>609</v>
@@ -4520,13 +4639,13 @@
         <v>16000</v>
       </c>
       <c r="F31" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I31">
         <v>13885.2</v>
@@ -4538,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -4546,10 +4665,10 @@
         <v>46107</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D32">
         <v>76.8</v>
@@ -4558,13 +4677,13 @@
         <v>125000</v>
       </c>
       <c r="F32" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I32">
         <v>13680</v>
@@ -4576,7 +4695,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -4584,10 +4703,10 @@
         <v>46107</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D33">
         <v>939</v>
@@ -4596,13 +4715,13 @@
         <v>13000</v>
       </c>
       <c r="F33" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G33" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H33" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -4614,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -4622,10 +4741,10 @@
         <v>46112</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="D34">
         <v>891</v>
@@ -4634,13 +4753,13 @@
         <v>13000</v>
       </c>
       <c r="F34" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G34" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="H34" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -4652,7 +4771,7 @@
         <v>34749</v>
       </c>
       <c r="L34" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -4667,37 +4786,37 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="H1" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="I1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="J1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="K1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -4705,10 +4824,10 @@
         <v>46020</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D2">
         <v>342.5</v>
@@ -4729,10 +4848,10 @@
         <v>-0.1306557134185975</v>
       </c>
       <c r="J2" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="K2" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -4740,10 +4859,10 @@
         <v>46020</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D3">
         <v>252.06</v>
@@ -4764,10 +4883,10 @@
         <v>0.04570815101532766</v>
       </c>
       <c r="J3" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="K3" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -4775,10 +4894,10 @@
         <v>46020</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D4">
         <v>149.5</v>
@@ -4799,10 +4918,10 @@
         <v>0.1072064281642808</v>
       </c>
       <c r="J4" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="K4" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4810,10 +4929,10 @@
         <v>46034</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D5">
         <v>130.5</v>
@@ -4834,10 +4953,10 @@
         <v>0.1541378248639367</v>
       </c>
       <c r="J5" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="K5" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -4845,10 +4964,10 @@
         <v>46034</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D6">
         <v>1770</v>
@@ -4869,10 +4988,10 @@
         <v>0.165468092149478</v>
       </c>
       <c r="J6" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="K6" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -4880,10 +4999,10 @@
         <v>46034</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D7">
         <v>177</v>
@@ -4904,10 +5023,10 @@
         <v>0.005391751781959497</v>
       </c>
       <c r="J7" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="K7" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -4915,10 +5034,10 @@
         <v>46045</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D8">
         <v>145</v>
@@ -4939,10 +5058,10 @@
         <v>-0.06411992221429286</v>
       </c>
       <c r="J8" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="K8" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -4950,10 +5069,10 @@
         <v>46045</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D9">
         <v>81.7</v>
@@ -4974,10 +5093,10 @@
         <v>-0.1117067603389773</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="K9" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -4985,10 +5104,10 @@
         <v>46058</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D10">
         <v>3700</v>
@@ -5009,10 +5128,10 @@
         <v>-0.03808464829509839</v>
       </c>
       <c r="J10" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="K10" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -5020,10 +5139,10 @@
         <v>46045</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D11">
         <v>1120</v>
@@ -5044,10 +5163,10 @@
         <v>0.2249450782634745</v>
       </c>
       <c r="J11" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="K11" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -5055,10 +5174,10 @@
         <v>46058</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D12">
         <v>489</v>
@@ -5079,10 +5198,10 @@
         <v>0.4597253106552202</v>
       </c>
       <c r="J12" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="K12" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -5090,10 +5209,10 @@
         <v>46083</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D13">
         <v>599</v>
@@ -5114,10 +5233,10 @@
         <v>-0.1153816579321046</v>
       </c>
       <c r="J13" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="K13" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -5125,10 +5244,10 @@
         <v>46094</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D14">
         <v>960</v>
@@ -5149,10 +5268,10 @@
         <v>-0.1311470477486248</v>
       </c>
       <c r="J14" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="K14" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -5160,10 +5279,10 @@
         <v>46094</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D15">
         <v>1450</v>
@@ -5184,10 +5303,10 @@
         <v>0.1072866854387671</v>
       </c>
       <c r="J15" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="K15" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -5195,10 +5314,10 @@
         <v>46094</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D16">
         <v>732</v>
@@ -5219,10 +5338,10 @@
         <v>0.2101025505867253</v>
       </c>
       <c r="J16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="K16" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -5240,19 +5359,19 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="F1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5260,10 +5379,10 @@
         <v>46024</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D2">
         <v>29000</v>
@@ -5280,10 +5399,10 @@
         <v>46024</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D3">
         <v>66000</v>
@@ -5300,10 +5419,10 @@
         <v>46024</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D4">
         <v>39000</v>
@@ -5320,10 +5439,10 @@
         <v>46027</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D5">
         <v>29000</v>
@@ -5340,10 +5459,10 @@
         <v>46027</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D6">
         <v>66000</v>
@@ -5360,10 +5479,10 @@
         <v>46027</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D7">
         <v>39000</v>
@@ -5380,10 +5499,10 @@
         <v>46028</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D8">
         <v>29000</v>
@@ -5400,10 +5519,10 @@
         <v>46028</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D9">
         <v>66000</v>
@@ -5420,10 +5539,10 @@
         <v>46028</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D10">
         <v>39000</v>
@@ -5440,10 +5559,10 @@
         <v>46029</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D11">
         <v>29000</v>
@@ -5460,10 +5579,10 @@
         <v>46029</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>66000</v>
@@ -5480,10 +5599,10 @@
         <v>46029</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D13">
         <v>39000</v>
@@ -5500,10 +5619,10 @@
         <v>46030</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="D14">
         <v>29000</v>
@@ -5520,10 +5639,10 @@
         <v>46030</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>66000</v>
@@ -5540,10 +5659,10 @@
         <v>46030</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D16">
         <v>39000</v>
@@ -5560,10 +5679,10 @@
         <v>46031</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D17">
         <v>66000</v>
@@ -5580,10 +5699,10 @@
         <v>46031</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D18">
         <v>39000</v>
@@ -5600,10 +5719,10 @@
         <v>46034</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D19">
         <v>66000</v>
@@ -5620,10 +5739,10 @@
         <v>46035</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D20">
         <v>5000</v>
@@ -5640,10 +5759,10 @@
         <v>46035</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D21">
         <v>76000</v>
@@ -5660,10 +5779,10 @@
         <v>46035</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D22">
         <v>56000</v>
@@ -5680,10 +5799,10 @@
         <v>46036</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D23">
         <v>5000</v>
@@ -5700,10 +5819,10 @@
         <v>46036</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D24">
         <v>76000</v>
@@ -5720,10 +5839,10 @@
         <v>46036</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D25">
         <v>56000</v>
@@ -5740,10 +5859,10 @@
         <v>46037</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D26">
         <v>5000</v>
@@ -5760,10 +5879,10 @@
         <v>46037</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D27">
         <v>76000</v>
@@ -5780,10 +5899,10 @@
         <v>46037</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D28">
         <v>56000</v>
@@ -5800,10 +5919,10 @@
         <v>46038</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D29">
         <v>5000</v>
@@ -5820,10 +5939,10 @@
         <v>46038</v>
       </c>
       <c r="B30" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D30">
         <v>76000</v>
@@ -5840,10 +5959,10 @@
         <v>46038</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D31">
         <v>56000</v>
@@ -5860,10 +5979,10 @@
         <v>46041</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D32">
         <v>5000</v>
@@ -5880,10 +5999,10 @@
         <v>46041</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D33">
         <v>76000</v>
@@ -5900,10 +6019,10 @@
         <v>46041</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D34">
         <v>56000</v>
@@ -5920,10 +6039,10 @@
         <v>46042</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D35">
         <v>5000</v>
@@ -5940,10 +6059,10 @@
         <v>46042</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D36">
         <v>76000</v>
@@ -5960,10 +6079,10 @@
         <v>46042</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D37">
         <v>56000</v>
@@ -5980,10 +6099,10 @@
         <v>46043</v>
       </c>
       <c r="B38" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D38">
         <v>5000</v>
@@ -6000,10 +6119,10 @@
         <v>46043</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D39">
         <v>76000</v>
@@ -6020,10 +6139,10 @@
         <v>46043</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C40" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D40">
         <v>56000</v>
@@ -6040,10 +6159,10 @@
         <v>46044</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D41">
         <v>5000</v>
@@ -6060,10 +6179,10 @@
         <v>46044</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D42">
         <v>56000</v>
@@ -6080,10 +6199,10 @@
         <v>46045</v>
       </c>
       <c r="B43" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D43">
         <v>5000</v>
@@ -6100,10 +6219,10 @@
         <v>46045</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D44">
         <v>56000</v>
@@ -6120,10 +6239,10 @@
         <v>46048</v>
       </c>
       <c r="B45" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D45">
         <v>68000</v>
@@ -6140,10 +6259,10 @@
         <v>46048</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D46">
         <v>8000</v>
@@ -6160,10 +6279,10 @@
         <v>46048</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D47">
         <v>121000</v>
@@ -6180,10 +6299,10 @@
         <v>46049</v>
       </c>
       <c r="B48" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D48">
         <v>68000</v>
@@ -6200,10 +6319,10 @@
         <v>46049</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D49">
         <v>8000</v>
@@ -6220,10 +6339,10 @@
         <v>46049</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D50">
         <v>121000</v>
@@ -6240,10 +6359,10 @@
         <v>46050</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C51" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D51">
         <v>68000</v>
@@ -6260,10 +6379,10 @@
         <v>46050</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C52" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D52">
         <v>8000</v>
@@ -6280,10 +6399,10 @@
         <v>46050</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D53">
         <v>121000</v>
@@ -6300,10 +6419,10 @@
         <v>46051</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D54">
         <v>68000</v>
@@ -6320,10 +6439,10 @@
         <v>46051</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D55">
         <v>8000</v>
@@ -6340,10 +6459,10 @@
         <v>46051</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C56" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D56">
         <v>121000</v>
@@ -6360,10 +6479,10 @@
         <v>46052</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D57">
         <v>68000</v>
@@ -6380,10 +6499,10 @@
         <v>46052</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D58">
         <v>8000</v>
@@ -6400,10 +6519,10 @@
         <v>46052</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C59" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D59">
         <v>121000</v>
@@ -6420,10 +6539,10 @@
         <v>46055</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C60" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D60">
         <v>8000</v>
@@ -6440,10 +6559,10 @@
         <v>46055</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D61">
         <v>121000</v>
@@ -6460,10 +6579,10 @@
         <v>46056</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D62">
         <v>8000</v>
@@ -6480,10 +6599,10 @@
         <v>46057</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C63" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D63">
         <v>8000</v>
@@ -6500,10 +6619,10 @@
         <v>46058</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D64">
         <v>8000</v>
@@ -6520,10 +6639,10 @@
         <v>46059</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C65" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D65">
         <v>2000</v>
@@ -6540,10 +6659,10 @@
         <v>46059</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D66">
         <v>8000</v>
@@ -6560,10 +6679,10 @@
         <v>46059</v>
       </c>
       <c r="B67" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D67">
         <v>20000</v>
@@ -6580,10 +6699,10 @@
         <v>46062</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D68">
         <v>2000</v>
@@ -6600,10 +6719,10 @@
         <v>46062</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D69">
         <v>8000</v>
@@ -6620,10 +6739,10 @@
         <v>46062</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D70">
         <v>20000</v>
@@ -6640,10 +6759,10 @@
         <v>46063</v>
       </c>
       <c r="B71" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C71" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D71">
         <v>2000</v>
@@ -6660,10 +6779,10 @@
         <v>46063</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C72" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D72">
         <v>8000</v>
@@ -6680,10 +6799,10 @@
         <v>46063</v>
       </c>
       <c r="B73" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D73">
         <v>20000</v>
@@ -6700,10 +6819,10 @@
         <v>46064</v>
       </c>
       <c r="B74" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C74" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D74">
         <v>2000</v>
@@ -6720,10 +6839,10 @@
         <v>46064</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C75" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D75">
         <v>8000</v>
@@ -6740,10 +6859,10 @@
         <v>46064</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D76">
         <v>20000</v>
@@ -6760,10 +6879,10 @@
         <v>46076</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C77" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D77">
         <v>2000</v>
@@ -6780,10 +6899,10 @@
         <v>46076</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C78" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D78">
         <v>8000</v>
@@ -6800,10 +6919,10 @@
         <v>46076</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C79" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D79">
         <v>20000</v>
@@ -6820,10 +6939,10 @@
         <v>46077</v>
       </c>
       <c r="B80" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D80">
         <v>2000</v>
@@ -6840,10 +6959,10 @@
         <v>46077</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C81" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D81">
         <v>8000</v>
@@ -6860,10 +6979,10 @@
         <v>46077</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C82" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D82">
         <v>20000</v>
@@ -6880,10 +6999,10 @@
         <v>46078</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C83" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D83">
         <v>2000</v>
@@ -6900,10 +7019,10 @@
         <v>46078</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C84" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D84">
         <v>8000</v>
@@ -6920,10 +7039,10 @@
         <v>46078</v>
       </c>
       <c r="B85" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C85" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D85">
         <v>20000</v>
@@ -6940,10 +7059,10 @@
         <v>46079</v>
       </c>
       <c r="B86" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C86" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D86">
         <v>2000</v>
@@ -6960,10 +7079,10 @@
         <v>46079</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C87" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D87">
         <v>8000</v>
@@ -6980,10 +7099,10 @@
         <v>46079</v>
       </c>
       <c r="B88" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D88">
         <v>20000</v>
@@ -7000,10 +7119,10 @@
         <v>46083</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C89" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D89">
         <v>2000</v>
@@ -7020,10 +7139,10 @@
         <v>46083</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D90">
         <v>8000</v>
@@ -7040,10 +7159,10 @@
         <v>46083</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C91" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D91">
         <v>20000</v>
@@ -7060,10 +7179,10 @@
         <v>46084</v>
       </c>
       <c r="B92" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C92" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D92">
         <v>11000</v>
@@ -7080,10 +7199,10 @@
         <v>46084</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C93" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D93">
         <v>8000</v>
@@ -7100,10 +7219,10 @@
         <v>46084</v>
       </c>
       <c r="B94" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C94" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D94">
         <v>20000</v>
@@ -7120,10 +7239,10 @@
         <v>46085</v>
       </c>
       <c r="B95" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C95" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D95">
         <v>11000</v>
@@ -7140,10 +7259,10 @@
         <v>46085</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="C96" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D96">
         <v>8000</v>
@@ -7160,10 +7279,10 @@
         <v>46085</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C97" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D97">
         <v>20000</v>
@@ -7180,10 +7299,10 @@
         <v>46086</v>
       </c>
       <c r="B98" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C98" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D98">
         <v>11000</v>
@@ -7200,10 +7319,10 @@
         <v>46087</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D99">
         <v>11000</v>
@@ -7220,10 +7339,10 @@
         <v>46090</v>
       </c>
       <c r="B100" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C100" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D100">
         <v>11000</v>
@@ -7240,10 +7359,10 @@
         <v>46097</v>
       </c>
       <c r="B101" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C101" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D101">
         <v>13000</v>
@@ -7260,10 +7379,10 @@
         <v>46097</v>
       </c>
       <c r="B102" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C102" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D102">
         <v>10000</v>
@@ -7280,10 +7399,10 @@
         <v>46097</v>
       </c>
       <c r="B103" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C103" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D103">
         <v>6000</v>
@@ -7300,10 +7419,10 @@
         <v>46098</v>
       </c>
       <c r="B104" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C104" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D104">
         <v>13000</v>
@@ -7320,10 +7439,10 @@
         <v>46098</v>
       </c>
       <c r="B105" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C105" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D105">
         <v>10000</v>
@@ -7340,10 +7459,10 @@
         <v>46098</v>
       </c>
       <c r="B106" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C106" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D106">
         <v>6000</v>
@@ -7360,10 +7479,10 @@
         <v>46099</v>
       </c>
       <c r="B107" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C107" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D107">
         <v>13000</v>
@@ -7380,10 +7499,10 @@
         <v>46099</v>
       </c>
       <c r="B108" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D108">
         <v>10000</v>
@@ -7400,10 +7519,10 @@
         <v>46099</v>
       </c>
       <c r="B109" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C109" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D109">
         <v>6000</v>
@@ -7420,10 +7539,10 @@
         <v>46100</v>
       </c>
       <c r="B110" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D110">
         <v>13000</v>
@@ -7440,10 +7559,10 @@
         <v>46100</v>
       </c>
       <c r="B111" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D111">
         <v>10000</v>
@@ -7460,10 +7579,10 @@
         <v>46100</v>
       </c>
       <c r="B112" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C112" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D112">
         <v>6000</v>
@@ -7480,10 +7599,10 @@
         <v>46101</v>
       </c>
       <c r="B113" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C113" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D113">
         <v>13000</v>
@@ -7500,10 +7619,10 @@
         <v>46101</v>
       </c>
       <c r="B114" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C114" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D114">
         <v>10000</v>
@@ -7520,10 +7639,10 @@
         <v>46101</v>
       </c>
       <c r="B115" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C115" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D115">
         <v>6000</v>
@@ -7540,10 +7659,10 @@
         <v>46104</v>
       </c>
       <c r="B116" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C116" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D116">
         <v>13000</v>
@@ -7560,10 +7679,10 @@
         <v>46104</v>
       </c>
       <c r="B117" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C117" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D117">
         <v>10000</v>
@@ -7580,10 +7699,10 @@
         <v>46104</v>
       </c>
       <c r="B118" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C118" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D118">
         <v>6000</v>
@@ -7600,10 +7719,10 @@
         <v>46105</v>
       </c>
       <c r="B119" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C119" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D119">
         <v>13000</v>
@@ -7620,10 +7739,10 @@
         <v>46105</v>
       </c>
       <c r="B120" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D120">
         <v>6000</v>
@@ -7640,10 +7759,10 @@
         <v>46106</v>
       </c>
       <c r="B121" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C121" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D121">
         <v>13000</v>
@@ -7660,10 +7779,10 @@
         <v>46106</v>
       </c>
       <c r="B122" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D122">
         <v>6000</v>
@@ -7680,10 +7799,10 @@
         <v>46107</v>
       </c>
       <c r="B123" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C123" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D123">
         <v>13000</v>
@@ -7700,10 +7819,10 @@
         <v>46107</v>
       </c>
       <c r="B124" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C124" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="D124">
         <v>6000</v>
@@ -7720,10 +7839,10 @@
         <v>46108</v>
       </c>
       <c r="B125" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D125">
         <v>13000</v>
@@ -7740,10 +7859,10 @@
         <v>46108</v>
       </c>
       <c r="B126" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C126" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D126">
         <v>16000</v>
@@ -7760,10 +7879,10 @@
         <v>46108</v>
       </c>
       <c r="B127" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C127" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D127">
         <v>125000</v>
@@ -7780,10 +7899,10 @@
         <v>46111</v>
       </c>
       <c r="B128" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C128" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D128">
         <v>13000</v>
@@ -7800,10 +7919,10 @@
         <v>46111</v>
       </c>
       <c r="B129" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C129" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D129">
         <v>16000</v>
@@ -7820,10 +7939,10 @@
         <v>46111</v>
       </c>
       <c r="B130" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D130">
         <v>125000</v>
@@ -7840,10 +7959,10 @@
         <v>46112</v>
       </c>
       <c r="B131" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C131" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D131">
         <v>13000</v>
@@ -7860,10 +7979,10 @@
         <v>46112</v>
       </c>
       <c r="B132" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C132" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D132">
         <v>16000</v>
@@ -7880,10 +7999,10 @@
         <v>46112</v>
       </c>
       <c r="B133" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C133" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D133">
         <v>125000</v>
@@ -7900,10 +8019,10 @@
         <v>46113</v>
       </c>
       <c r="B134" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C134" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D134">
         <v>16000</v>
@@ -7920,10 +8039,10 @@
         <v>46113</v>
       </c>
       <c r="B135" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C135" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D135">
         <v>125000</v>
@@ -7940,10 +8059,10 @@
         <v>46114</v>
       </c>
       <c r="B136" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C136" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D136">
         <v>16000</v>
@@ -7960,10 +8079,10 @@
         <v>46114</v>
       </c>
       <c r="B137" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C137" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D137">
         <v>125000</v>
@@ -7980,10 +8099,10 @@
         <v>46119</v>
       </c>
       <c r="B138" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C138" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D138">
         <v>16000</v>
@@ -8000,10 +8119,10 @@
         <v>46119</v>
       </c>
       <c r="B139" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C139" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D139">
         <v>125000</v>
@@ -8020,10 +8139,10 @@
         <v>46120</v>
       </c>
       <c r="B140" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C140" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D140">
         <v>16000</v>
@@ -8040,10 +8159,10 @@
         <v>46120</v>
       </c>
       <c r="B141" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C141" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D141">
         <v>125000</v>
@@ -8060,10 +8179,10 @@
         <v>46121</v>
       </c>
       <c r="B142" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C142" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D142">
         <v>16000</v>
@@ -8080,10 +8199,10 @@
         <v>46121</v>
       </c>
       <c r="B143" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D143">
         <v>125000</v>
@@ -8100,10 +8219,10 @@
         <v>46122</v>
       </c>
       <c r="B144" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C144" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="D144">
         <v>16000</v>
@@ -8120,10 +8239,10 @@
         <v>46122</v>
       </c>
       <c r="B145" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C145" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="D145">
         <v>125000</v>
